--- a/business_forms/002_student_enrollment_amp_release_form_littlest_learners--business_forms.xlsx
+++ b/business_forms/002_student_enrollment_amp_release_form_littlest_learners--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>student_enrollment_form</t>
+          <t>Student Enrollment Form</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>student_name</t>
+          <t>Student Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>student_email</t>
+          <t>Student Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>student_phone</t>
+          <t>Student Phone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>enrollment_date</t>
+          <t>Enrollment Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>release_date</t>
+          <t>program_name</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>release_date</t>
+          <t>Program Name</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,35 +658,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>program_name</t>
+          <t>program_name_camp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>program_name</t>
+          <t>Program Name (Camp)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>program_name_camp</t>
+          <t>program_name_camp_other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>program_name</t>
+          <t>Other (Camp)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>program_price</t>
+          <t>Program Price</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>parent_name</t>
+          <t>Parent Name</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>parent_email</t>
+          <t>Parent Email</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>parent_phone</t>
+          <t>Parent Phone</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>select_program</t>
+          <t>program</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>program</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,41 +842,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>select_program_other</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>select_other</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_of_day</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,90 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>time_of_day</t>
+          <t>other_note</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>time_of_day</t>
+          <t>Other Note</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>time_of_day_note</t>
+          <t>student_id</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>time_of_day_note</t>
+          <t>Student ID</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>time_of_day_other</t>
+          <t>student_id_camp</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Student ID (Camp)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>time_of_day_other_note</t>
+          <t>student_id_other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>other_note</t>
+          <t>Other Student ID</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>student_id_camp</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>student_id_other</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>student_id_other_note</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>other_note</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1101,7 +1009,7 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,75 +1034,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_program_choices</t>
+          <t>program_name_camp_other_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sprouts</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sprouts</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_program_choices</t>
+          <t>program_name_camp_other_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>camp</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_program_other_choices</t>
+          <t>program_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>sprouts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sprouts</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_program_other_choices</t>
+          <t>program_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>camp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Camp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time_of_day_other_choices</t>
+          <t>other_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1119,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time_of_day_other_choices</t>
+          <t>other_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
